--- a/glasses/1158042982-1/1158042982-1.xlsx
+++ b/glasses/1158042982-1/1158042982-1.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
